--- a/states_reason.xlsx
+++ b/states_reason.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Inlogic_Projects\AI_Testing\ado_board_deva\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B44941F6-E17F-4127-94B3-3B23E59CDB5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F2FA5B2-9C7C-4725-8733-BB9D8F00D4F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -72,9 +72,6 @@
     <t>Completed</t>
   </si>
   <si>
-    <t>Ready for Release</t>
-  </si>
-  <si>
     <t>Code Review</t>
   </si>
   <si>
@@ -118,6 +115,9 @@
   </si>
   <si>
     <t>To Do</t>
+  </si>
+  <si>
+    <t>Ready to Release</t>
   </si>
 </sst>
 </file>
@@ -697,7 +697,7 @@
         <v>4</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -717,7 +717,7 @@
         <v>5</v>
       </c>
       <c r="H4" s="6" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -734,7 +734,7 @@
         <v>8</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="H5" s="7" t="s">
         <v>9</v>
@@ -757,7 +757,7 @@
         <v>9</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -782,49 +782,49 @@
     </row>
     <row r="8" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B8" s="16" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C8" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="9" t="s">
         <v>15</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="E8" s="9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="26" t="s">
         <v>16</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="H8" s="17" t="s">
         <v>16</v>
-      </c>
-      <c r="F8" s="26" t="s">
-        <v>17</v>
-      </c>
-      <c r="H8" s="17" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="9" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B9" s="18" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="D9" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="19" t="s">
-        <v>14</v>
-      </c>
-      <c r="D9" s="9" t="s">
-        <v>18</v>
-      </c>
       <c r="E9" s="22" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F9" s="27"/>
     </row>
     <row r="10" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="20"/>
       <c r="C10" s="10" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E10" s="22" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F10" s="28"/>
     </row>
@@ -843,10 +843,10 @@
       <c r="B12" s="20"/>
       <c r="C12" s="14"/>
       <c r="D12" s="13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E12" s="23" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F12" s="28"/>
     </row>
@@ -854,10 +854,10 @@
       <c r="B13" s="20"/>
       <c r="C13" s="14"/>
       <c r="D13" s="13" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E13" s="23" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F13" s="28"/>
     </row>
@@ -865,10 +865,10 @@
       <c r="B14" s="20"/>
       <c r="C14" s="14"/>
       <c r="D14" s="19" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F14" s="28"/>
     </row>
@@ -876,10 +876,10 @@
       <c r="B15" s="20"/>
       <c r="C15" s="14"/>
       <c r="D15" s="21" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E15" s="25" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F15" s="28"/>
     </row>
@@ -887,10 +887,10 @@
       <c r="B16" s="20"/>
       <c r="C16" s="14"/>
       <c r="D16" s="21" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E16" s="25" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F16" s="28"/>
     </row>
@@ -898,10 +898,10 @@
       <c r="B17" s="20"/>
       <c r="C17" s="14"/>
       <c r="D17" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="E17" s="25" t="s">
         <v>25</v>
-      </c>
-      <c r="E17" s="25" t="s">
-        <v>26</v>
       </c>
       <c r="F17" s="28"/>
     </row>
@@ -910,7 +910,7 @@
       <c r="C18" s="14"/>
       <c r="D18" s="14"/>
       <c r="E18" s="25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F18" s="29"/>
     </row>

--- a/states_reason.xlsx
+++ b/states_reason.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Inlogic_Projects\AI_Testing\ado_board_deva\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F2FA5B2-9C7C-4725-8733-BB9D8F00D4F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7003096-9076-4EC0-AD64-A5484A0780F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="31">
   <si>
     <t>EPIC</t>
   </si>
@@ -817,7 +817,7 @@
     </row>
     <row r="10" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B10" s="20"/>
-      <c r="C10" s="10" t="s">
+      <c r="C10" s="26" t="s">
         <v>16</v>
       </c>
       <c r="D10" s="9" t="s">
@@ -908,7 +908,9 @@
     <row r="18" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B18" s="20"/>
       <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
+      <c r="D18" s="26" t="s">
+        <v>16</v>
+      </c>
       <c r="E18" s="25" t="s">
         <v>24</v>
       </c>

--- a/states_reason.xlsx
+++ b/states_reason.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Inlogic_Projects\AI_Testing\ado_board_deva\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7003096-9076-4EC0-AD64-A5484A0780F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADEC04A3-3DE7-4F14-AAE0-6624D3A83F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -221,64 +221,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="2">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top style="medium">
-        <color indexed="64"/>
-      </top>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -296,99 +244,44 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -669,7 +562,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:H18"/>
+  <dimension ref="B3:H18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
@@ -679,242 +572,241 @@
     <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="3" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="1" t="s">
+    <row r="3" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B3" s="11" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="E3" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="1" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="4" t="s">
+    <row r="4" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B4" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="E4" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="4" t="s">
+    <row r="5" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B5" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E5" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="H5" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="8" t="s">
+    <row r="6" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B6" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="9" t="s">
+      <c r="C6" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="D6" s="9" t="s">
+      <c r="D6" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="9" t="s">
+      <c r="E6" s="13" t="s">
         <v>10</v>
       </c>
-      <c r="F6" s="8" t="s">
+      <c r="F6" s="13" t="s">
         <v>9</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="12" t="s">
+    <row r="7" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B7" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D7" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="E7" s="9" t="s">
+      <c r="E7" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="F7" s="16" t="s">
+      <c r="F7" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="H7" s="15" t="s">
+      <c r="H7" s="5" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="8" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="16" t="s">
+    <row r="8" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B8" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="13" t="s">
+      <c r="C8" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="9" t="s">
+      <c r="D8" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="9" t="s">
+      <c r="E8" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="26" t="s">
+      <c r="F8" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="H8" s="17" t="s">
+      <c r="H8" s="6" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="18" t="s">
+    <row r="9" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B9" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="15" t="s">
+      <c r="C9" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="9" t="s">
+      <c r="D9" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="E9" s="22" t="s">
+      <c r="E9" s="13" t="s">
         <v>17</v>
       </c>
-      <c r="F9" s="27"/>
-    </row>
-    <row r="10" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B10" s="20"/>
-      <c r="C10" s="26" t="s">
+      <c r="F9" s="7"/>
+    </row>
+    <row r="10" spans="2:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B10" s="8"/>
+      <c r="C10" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="9" t="s">
+      <c r="D10" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="22" t="s">
+      <c r="E10" s="13" t="s">
         <v>18</v>
       </c>
-      <c r="F10" s="28"/>
-    </row>
-    <row r="11" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B11" s="20"/>
-      <c r="C11" s="10"/>
-      <c r="D11" s="13" t="s">
+      <c r="F10" s="8"/>
+    </row>
+    <row r="11" spans="2:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B11" s="8"/>
+      <c r="C11" s="16"/>
+      <c r="D11" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="23" t="s">
+      <c r="E11" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F11" s="28"/>
-    </row>
-    <row r="12" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B12" s="20"/>
-      <c r="C12" s="14"/>
-      <c r="D12" s="13" t="s">
+      <c r="F11" s="8"/>
+    </row>
+    <row r="12" spans="2:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="E12" s="23" t="s">
+      <c r="E12" s="14" t="s">
         <v>19</v>
       </c>
-      <c r="F12" s="28"/>
-    </row>
-    <row r="13" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B13" s="20"/>
-      <c r="C13" s="14"/>
-      <c r="D13" s="13" t="s">
+      <c r="F12" s="8"/>
+    </row>
+    <row r="13" spans="2:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B13" s="8"/>
+      <c r="C13" s="8"/>
+      <c r="D13" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="E13" s="23" t="s">
+      <c r="E13" s="14" t="s">
         <v>20</v>
       </c>
-      <c r="F13" s="28"/>
-    </row>
-    <row r="14" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B14" s="20"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="19" t="s">
+      <c r="F13" s="8"/>
+    </row>
+    <row r="14" spans="2:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B14" s="8"/>
+      <c r="C14" s="8"/>
+      <c r="D14" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="E14" s="24" t="s">
+      <c r="E14" s="15" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="28"/>
-    </row>
-    <row r="15" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B15" s="20"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="21" t="s">
+      <c r="F14" s="8"/>
+    </row>
+    <row r="15" spans="2:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B15" s="8"/>
+      <c r="C15" s="8"/>
+      <c r="D15" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="E15" s="25" t="s">
+      <c r="E15" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="F15" s="28"/>
-    </row>
-    <row r="16" spans="2:8" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B16" s="20"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="21" t="s">
+      <c r="F15" s="8"/>
+    </row>
+    <row r="16" spans="2:8" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B16" s="8"/>
+      <c r="C16" s="8"/>
+      <c r="D16" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="E16" s="25" t="s">
+      <c r="E16" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F16" s="28"/>
-    </row>
-    <row r="17" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B17" s="20"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="21" t="s">
+      <c r="F16" s="8"/>
+    </row>
+    <row r="17" spans="2:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B17" s="8"/>
+      <c r="C17" s="8"/>
+      <c r="D17" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="E17" s="25" t="s">
+      <c r="E17" s="10" t="s">
         <v>25</v>
       </c>
-      <c r="F17" s="28"/>
-    </row>
-    <row r="18" spans="2:6" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B18" s="20"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="26" t="s">
+      <c r="F17" s="8"/>
+    </row>
+    <row r="18" spans="2:6" ht="16.5" x14ac:dyDescent="0.3">
+      <c r="B18" s="8"/>
+      <c r="C18" s="8"/>
+      <c r="D18" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="E18" s="25" t="s">
+      <c r="E18" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="F18" s="29"/>
+      <c r="F18" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/states_reason.xlsx
+++ b/states_reason.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Inlogic_Projects\AI_Testing\ado_board_deva\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ADEC04A3-3DE7-4F14-AAE0-6624D3A83F2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DA10F2C-3047-46BA-A450-243B44FB4B87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="32">
   <si>
     <t>EPIC</t>
   </si>
@@ -118,6 +118,9 @@
   </si>
   <si>
     <t>Ready to Release</t>
+  </si>
+  <si>
+    <t>States</t>
   </si>
 </sst>
 </file>
@@ -221,7 +224,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -244,11 +247,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -281,6 +293,9 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -562,7 +577,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B3:H18"/>
+  <dimension ref="B2:H18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="10.85546875" bestFit="1" customWidth="1"/>
@@ -572,6 +587,15 @@
     <col min="8" max="8" width="13.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
+    <row r="2" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B2" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+    </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" s="11" t="s">
         <v>0</v>
@@ -809,6 +833,10 @@
       <c r="F18" s="9"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:F2"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>